--- a/artfynd/A 17956-2023 artfynd.xlsx
+++ b/artfynd/A 17956-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17956-2023 artfynd.xlsx
+++ b/artfynd/A 17956-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104024713</v>
+        <v>104024739</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544159.9126391591</v>
+        <v>544021</v>
       </c>
       <c r="R2" t="n">
-        <v>7132683.50401567</v>
+        <v>7132582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Rönn</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104024819</v>
+        <v>104024813</v>
       </c>
       <c r="B3" t="n">
-        <v>90174</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2014</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543947.3953759004</v>
+        <v>543900</v>
       </c>
       <c r="R3" t="n">
-        <v>7132414.898714267</v>
+        <v>7132449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,11 +877,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Björkhögstubbe</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -910,6 +890,576 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104024819</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92732</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Klingermyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>543947</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7132415</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-08-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-08-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104024784</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Klingermyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>544179</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7132635</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-08-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-08-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104024768</v>
+      </c>
+      <c r="B6" t="n">
+        <v>87170</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Klingermyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>544188</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7132604</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-08-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-08-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104024815</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79583</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Klingermyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>544202</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7132648</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-08-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-08-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104024713</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Klingermyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>544160</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7132683</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Rönn</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 17956-2023 artfynd.xlsx
+++ b/artfynd/A 17956-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104024739</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104024813</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104024819</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104024784</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104024768</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104024815</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,8 +1499,22 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104024713</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>